--- a/artfynd/A 5291-2024 artfynd.xlsx
+++ b/artfynd/A 5291-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136439388</v>
       </c>
       <c r="B2" t="n">
-        <v>99380</v>
+        <v>99383</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136439389</v>
       </c>
       <c r="B3" t="n">
-        <v>102790</v>
+        <v>102793</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136439390</v>
       </c>
       <c r="B4" t="n">
-        <v>102790</v>
+        <v>102793</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5291-2024 artfynd.xlsx
+++ b/artfynd/A 5291-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136439388</v>
       </c>
       <c r="B2" t="n">
-        <v>99383</v>
+        <v>99384</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136439389</v>
       </c>
       <c r="B3" t="n">
-        <v>102793</v>
+        <v>102794</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136439390</v>
       </c>
       <c r="B4" t="n">
-        <v>102793</v>
+        <v>102794</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5291-2024 artfynd.xlsx
+++ b/artfynd/A 5291-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136439388</v>
       </c>
       <c r="B2" t="n">
-        <v>99384</v>
+        <v>99389</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136439389</v>
       </c>
       <c r="B3" t="n">
-        <v>102794</v>
+        <v>102799</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136439390</v>
       </c>
       <c r="B4" t="n">
-        <v>102794</v>
+        <v>102799</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5291-2024 artfynd.xlsx
+++ b/artfynd/A 5291-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136439388</v>
       </c>
       <c r="B2" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136439389</v>
       </c>
       <c r="B3" t="n">
-        <v>102799</v>
+        <v>102801</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136439390</v>
       </c>
       <c r="B4" t="n">
-        <v>102799</v>
+        <v>102801</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5291-2024 artfynd.xlsx
+++ b/artfynd/A 5291-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136439388</v>
       </c>
       <c r="B2" t="n">
-        <v>99391</v>
+        <v>99397</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136439389</v>
       </c>
       <c r="B3" t="n">
-        <v>102801</v>
+        <v>102807</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136439390</v>
       </c>
       <c r="B4" t="n">
-        <v>102801</v>
+        <v>102807</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5291-2024 artfynd.xlsx
+++ b/artfynd/A 5291-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136439388</v>
       </c>
       <c r="B2" t="n">
-        <v>99397</v>
+        <v>99399</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136439389</v>
       </c>
       <c r="B3" t="n">
-        <v>102807</v>
+        <v>102809</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136439390</v>
       </c>
       <c r="B4" t="n">
-        <v>102807</v>
+        <v>102809</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5291-2024 artfynd.xlsx
+++ b/artfynd/A 5291-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136439388</v>
       </c>
       <c r="B2" t="n">
-        <v>99399</v>
+        <v>99400</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136439389</v>
       </c>
       <c r="B3" t="n">
-        <v>102809</v>
+        <v>102810</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136439390</v>
       </c>
       <c r="B4" t="n">
-        <v>102809</v>
+        <v>102810</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
